--- a/Kỹ Thuật lập trình/C/09. DEBUGGING & PROFILING.xlsx
+++ b/Kỹ Thuật lập trình/C/09. DEBUGGING & PROFILING.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Document\02.Study\Linux\Kỹ Thuật lập trình\C\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORK\Home\C\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11610" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Mục Lục" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="345">
   <si>
     <t>🔍 DEBUGGING &amp; PROFILING</t>
   </si>
@@ -49,7 +49,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -66,7 +66,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -83,7 +83,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -136,7 +136,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -153,7 +153,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -170,7 +170,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -226,7 +226,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -243,7 +243,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -525,7 +525,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -544,7 +544,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -561,7 +561,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -572,7 +572,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -588,7 +588,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -604,7 +604,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -620,7 +620,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -637,7 +637,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -648,7 +648,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -672,7 +672,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -691,7 +691,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -715,7 +715,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -734,7 +734,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -758,7 +758,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -770,7 +770,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -781,7 +781,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -805,7 +805,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -829,7 +829,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -846,7 +846,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -857,7 +857,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -881,7 +881,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -905,7 +905,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -929,7 +929,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -953,7 +953,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -977,7 +977,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1001,7 +1001,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1017,7 +1017,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1033,7 +1033,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1049,7 +1049,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1065,7 +1065,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1081,7 +1081,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1316,7 +1316,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1332,7 +1332,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1348,7 +1348,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1364,7 +1364,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1381,7 +1381,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1392,7 +1392,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1409,7 +1409,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1420,7 +1420,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1432,7 +1432,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1443,7 +1443,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1467,7 +1467,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1484,7 +1484,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1495,7 +1495,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1507,7 +1507,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1518,7 +1518,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1542,7 +1542,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1559,7 +1559,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1570,7 +1570,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1587,7 +1587,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1598,7 +1598,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1622,7 +1622,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1638,7 +1638,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1655,7 +1655,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1666,7 +1666,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1683,7 +1683,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1694,7 +1694,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1711,7 +1711,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1722,7 +1722,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1739,7 +1739,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1750,7 +1750,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1767,7 +1767,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1778,7 +1778,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1795,7 +1795,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1806,7 +1806,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1818,7 +1818,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1829,7 +1829,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1845,7 +1845,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1857,7 +1857,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1868,7 +1868,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1884,7 +1884,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1900,7 +1900,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1916,7 +1916,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1932,7 +1932,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1948,7 +1948,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1964,7 +1964,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -1973,31 +1973,1088 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">👉 Bạn có muốn mình tiếp tục làm </t>
+    <t>3. Performance Profiling (Phân tích hiệu năng)</t>
+  </si>
+  <si>
+    <t>3.1 Profiling Tools (Công cụ đo đạc)</t>
+  </si>
+  <si>
+    <t>Công cụ profiling cổ điển đi kèm GNU binutils.</t>
+  </si>
+  <si>
+    <t>gcc -pg program.c -o program</t>
+  </si>
+  <si>
+    <t>gprof ./program gmon.out &gt; report.txt</t>
+  </si>
+  <si>
+    <t>Kết quả</t>
+  </si>
+  <si>
+    <t>Thống kê % thời gian dùng trong mỗi hàm.</t>
+  </si>
+  <si>
+    <t>Call graph: hàm nào gọi hàm nào.</t>
+  </si>
+  <si>
+    <t>Không phù hợp với multithreading (pthread).</t>
+  </si>
+  <si>
+    <t>Overhead cao, kết quả dễ bị sai lệch.</t>
+  </si>
+  <si>
+    <t>Nhanh chóng xác định “hàm nóng” (hotspot).</t>
+  </si>
+  <si>
+    <t>Công cụ hiện đại, low-overhead, dùng hardware performance counters.</t>
+  </si>
+  <si>
+    <t>Theo dõi CPU, cache miss, system calls, context switch.</t>
+  </si>
+  <si>
+    <t>perf stat ./program             # thống kê chung</t>
+  </si>
+  <si>
+    <t>perf record ./program           # ghi dữ liệu</t>
+  </si>
+  <si>
+    <t>perf report                     # hiển thị kết quả</t>
+  </si>
+  <si>
+    <t>Ví dụ</t>
+  </si>
+  <si>
+    <t>Xem thống kê cache misses, branch misses:</t>
+  </si>
+  <si>
+    <t>perf stat -e cache-misses,branches,branch-misses ./program</t>
+  </si>
+  <si>
+    <t>Yêu cầu quyền root cho một số event.</t>
+  </si>
+  <si>
+    <t>Output nhiều, cần lọc chọn metric phù hợp.</t>
+  </si>
+  <si>
+    <t>Phân tích bottleneck phần cứng.</t>
+  </si>
+  <si>
+    <t>Tối ưu thuật toán / memory access.</t>
+  </si>
+  <si>
+    <t>3.1.3 Intel VTune Profiler</t>
+  </si>
+  <si>
+    <t>Công cụ thương mại (Intel), hỗ trợ Linux/Windows.</t>
+  </si>
+  <si>
+    <t>Cách dùng cơ bản</t>
+  </si>
+  <si>
+    <t>Chạy trong GUI hoặc CLI:</t>
+  </si>
+  <si>
+    <t>vtune -collect hotspots ./program</t>
+  </si>
+  <si>
+    <t>Tính năng</t>
+  </si>
+  <si>
+    <t>Hotspots (CPU-bound).</t>
+  </si>
+  <si>
+    <t>Memory access analysis.</t>
+  </si>
+  <si>
+    <t>Threading/concurrency analysis.</t>
+  </si>
+  <si>
+    <t>Cần CPU Intel để tối ưu nhất (hỗ trợ AMD hạn chế).</t>
+  </si>
+  <si>
+    <t>Trả phí bản đầy đủ (có bản free hạn chế).</t>
+  </si>
+  <si>
+    <t>Tối ưu HPC (High Performance Computing).</t>
+  </si>
+  <si>
+    <t>3.1.4 Custom Timing Code</t>
+  </si>
+  <si>
+    <t>#include &lt;time.h&gt;</t>
+  </si>
+  <si>
+    <t>double now_sec(){</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    struct timespec t;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    clock_gettime(CLOCK_MONOTONIC, &amp;t);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    return t.tv_sec + t.tv_nsec*1e-9;</t>
+  </si>
+  <si>
+    <t>int main(){</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    double t1 = now_sec();</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // code cần đo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    double t2 = now_sec();</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Elapsed = %f sec\n", t2 - t1);</t>
+  </si>
+  <si>
+    <t>Resolution phụ thuộc hệ điều hành.</t>
+  </si>
+  <si>
+    <t>Nhiễu từ context switch.</t>
+  </si>
+  <si>
+    <t>Đo micro-benchmark cho hàm riêng lẻ.</t>
+  </si>
+  <si>
+    <t>So sánh phiên bản code tối ưu hóa.</t>
+  </si>
+  <si>
+    <t>3.2 Performance Metrics (Chỉ số hiệu năng)</t>
+  </si>
+  <si>
+    <t>3.2.1 CPU Usage Profiling</t>
+  </si>
+  <si>
+    <t>Đo % thời gian CPU dành cho từng hàm, tiến trình, thread.</t>
+  </si>
+  <si>
+    <t>perf top -p &lt;pid&gt;</t>
+  </si>
+  <si>
+    <t>→ hiển thị live “hàm ngốn CPU nhất”.</t>
+  </si>
+  <si>
+    <t>CPU-bound ≠ bottleneck thực sự (có thể là do cache miss).</t>
+  </si>
+  <si>
+    <t>3.2.2 Memory Usage Analysis</t>
+  </si>
+  <si>
+    <t>Ví dụ với Massif:</t>
+  </si>
+  <si>
+    <t>valgrind --tool=massif ./program</t>
+  </si>
+  <si>
+    <t>ms_print massif.out.xxxx</t>
+  </si>
+  <si>
+    <t>Xác định chỗ cấp phát thừa.</t>
+  </si>
+  <si>
+    <t>Tối ưu thuật toán giảm heap allocation.</t>
+  </si>
+  <si>
+    <t>3.2.3 Cache Performance</t>
+  </si>
+  <si>
+    <t>Cache miss thường là nguyên nhân chính làm chậm chương trình.</t>
+  </si>
+  <si>
+    <t>perf stat -e cache-references,cache-misses ./program</t>
+  </si>
+  <si>
+    <t>→ cho tỷ lệ miss %.</t>
+  </si>
+  <si>
+    <t>High cache miss → code có access pattern kém (truy cập không liên tục).</t>
+  </si>
+  <si>
+    <t>Khắc phục bằng:</t>
+  </si>
+  <si>
+    <t>Blocking/tile trong matrix multiplication.</t>
+  </si>
+  <si>
+    <t>3.2.4 System Call Analysis</t>
+  </si>
+  <si>
+    <t>Xem chương trình tốn thời gian ở system call nào (I/O bound).</t>
+  </si>
+  <si>
+    <t>strace -c ./program</t>
+  </si>
+  <si>
+    <t>→ báo cáo thời gian, số lần gọi mỗi syscall.</t>
+  </si>
+  <si>
+    <t>3.3 Checklist ứng dụng thực tế</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3.1.1 </t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>3. Build &amp; Compilation Debugging</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (warnings, optimization levels, linker debug, symbol visibility, ABI issues) theo format chi tiết tương tự không?</t>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>gprof</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> profiler</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dựa vào </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>instrumentation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (compiler chèn code thống kê) → tốn overhead.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Biên dịch với </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>-pg</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2. Chạy chương trình: sinh file </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>gmon.out</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3. Phân tích bằng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>gprof</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Phân tích chương trình </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>single-thread C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> cổ điển.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3.1.2 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>perf</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tool (Linux)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dùng cho tối ưu chuyên sâu: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>vectorization, memory bandwidth, threading efficiency</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Debug </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>false sharing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cache line contention</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dùng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>perf top</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>htop</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>gprof</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ví dụ với </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>perf top</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Đo lượng </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>heap allocation/free</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, rò rỉ bộ nhớ.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Công cụ: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>valgrind --tool=massif</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>heaptrack</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>mprof</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dùng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>perf stat -e cache-references,cache-misses</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Locality of reference</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (dùng array liên tục thay linked list).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Công cụ: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>strace -c</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>perf trace</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ví dụ với </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>strace</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Xác định chương trình bị chậm do I/O: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>read</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>write</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>fsync</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>poll</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Hữu ích khi debug </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>server I/O</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Bước 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Dùng profiler nhẹ (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>perf stat</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>time</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) để check tổng quan.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Bước 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Nếu CPU-bound → phân tích hotspots (gprof/perf/VTune).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Bước 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Nếu Memory-bound → dùng massif/heaptrack.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Bước 4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Check cache misses &amp; system calls nếu nghi ngờ bottleneck.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Bước 5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Đo lại bằng custom timing để xác minh tối ưu hóa.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Khi không có profiler, có thể dùng </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>đo thời gian thủ công</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dùng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>clock_gettime()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>gettimeofday()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>rdtsc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (x86).</t>
     </r>
   </si>
 </sst>
@@ -2005,11 +3062,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="8">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="163"/>
       <scheme val="minor"/>
@@ -2017,7 +3074,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="163"/>
       <scheme val="minor"/>
@@ -2026,7 +3083,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="163"/>
       <scheme val="minor"/>
@@ -2035,7 +3092,7 @@
       <b/>
       <sz val="18"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="163"/>
       <scheme val="minor"/>
@@ -2044,7 +3101,7 @@
       <b/>
       <sz val="13.5"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="163"/>
       <scheme val="minor"/>
@@ -2057,17 +3114,45 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="163"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="163"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="5">
@@ -2145,7 +3230,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2197,6 +3282,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2478,9 +3572,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:AG21"/>
-  <sheetFormatPr defaultColWidth="3" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="3" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:33" ht="15" thickBot="1"/>
+    <row r="1" spans="2:33" ht="15.75" thickBot="1"/>
     <row r="2" spans="2:33" ht="24" thickBot="1">
       <c r="B2" s="5" t="s">
         <v>0</v>
@@ -2517,7 +3611,7 @@
       <c r="AF2" s="1"/>
       <c r="AG2" s="1"/>
     </row>
-    <row r="3" spans="2:33" ht="17.25">
+    <row r="3" spans="2:33" ht="18">
       <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
@@ -2557,7 +3651,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="2:33" ht="15">
+    <row r="4" spans="2:33">
       <c r="B4" s="2" t="s">
         <v>4</v>
       </c>
@@ -2791,7 +3885,7 @@
       <c r="AF9" s="1"/>
       <c r="AG9" s="2"/>
     </row>
-    <row r="10" spans="2:33" ht="15">
+    <row r="10" spans="2:33">
       <c r="B10" s="2" t="s">
         <v>19</v>
       </c>
@@ -3027,7 +4121,7 @@
       <c r="AF15" s="1"/>
       <c r="AG15" s="1"/>
     </row>
-    <row r="16" spans="2:33" ht="15">
+    <row r="16" spans="2:33">
       <c r="B16" s="2"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -3063,7 +4157,7 @@
       <c r="AF16" s="1"/>
       <c r="AG16" s="1"/>
     </row>
-    <row r="17" spans="2:33" ht="15">
+    <row r="17" spans="2:33">
       <c r="B17" s="2" t="s">
         <v>36</v>
       </c>
@@ -3259,7 +4353,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BF62"/>
-  <sheetFormatPr defaultColWidth="3" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="3" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="16384" width="3" style="11"/>
   </cols>
@@ -3274,7 +4368,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:58" ht="15">
+    <row r="3" spans="1:58">
       <c r="A3" s="19" t="s">
         <v>47</v>
       </c>
@@ -3306,7 +4400,7 @@
       <c r="BE3" s="20"/>
       <c r="BF3" s="20"/>
     </row>
-    <row r="4" spans="1:58" ht="15">
+    <row r="4" spans="1:58">
       <c r="A4" s="13" t="s">
         <v>123</v>
       </c>
@@ -3317,7 +4411,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="5" spans="1:58" ht="15">
+    <row r="5" spans="1:58">
       <c r="A5" s="13" t="s">
         <v>124</v>
       </c>
@@ -3330,7 +4424,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="7" spans="1:58" ht="15">
+    <row r="7" spans="1:58">
       <c r="A7" s="19" t="s">
         <v>48</v>
       </c>
@@ -3368,7 +4462,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="9" spans="1:58" ht="15">
+    <row r="9" spans="1:58">
       <c r="A9" s="9" t="s">
         <v>125</v>
       </c>
@@ -3379,7 +4473,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:58" ht="15">
+    <row r="10" spans="1:58">
       <c r="A10" s="9" t="s">
         <v>126</v>
       </c>
@@ -3387,7 +4481,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="11" spans="1:58" ht="15">
+    <row r="11" spans="1:58">
       <c r="A11" s="9" t="s">
         <v>127</v>
       </c>
@@ -3403,7 +4497,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="1:58" ht="15">
+    <row r="13" spans="1:58">
       <c r="A13" s="8" t="s">
         <v>50</v>
       </c>
@@ -3436,7 +4530,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="15" spans="1:58" ht="15">
+    <row r="15" spans="1:58">
       <c r="A15" s="15" t="s">
         <v>52</v>
       </c>
@@ -3486,13 +4580,13 @@
         <v>58</v>
       </c>
     </row>
-    <row r="22" spans="1:50" ht="15" thickBot="1"/>
+    <row r="22" spans="1:50" ht="15.75" thickBot="1"/>
     <row r="23" spans="1:50" s="17" customFormat="1" ht="15.75" thickBot="1">
       <c r="A23" s="16" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="24" spans="1:50" ht="15">
+    <row r="24" spans="1:50">
       <c r="A24" s="21" t="s">
         <v>80</v>
       </c>
@@ -3530,7 +4624,7 @@
       <c r="AW24" s="22"/>
       <c r="AX24" s="22"/>
     </row>
-    <row r="25" spans="1:50" ht="15">
+    <row r="25" spans="1:50">
       <c r="A25" s="13" t="s">
         <v>131</v>
       </c>
@@ -3562,7 +4656,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="29" spans="1:50" ht="15">
+    <row r="29" spans="1:50">
       <c r="A29" s="21" t="s">
         <v>82</v>
       </c>
@@ -3611,7 +4705,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="32" spans="1:50" ht="15">
+    <row r="32" spans="1:50">
       <c r="A32" s="15" t="s">
         <v>85</v>
       </c>
@@ -3632,7 +4726,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="36" spans="1:43" ht="15">
+    <row r="36" spans="1:43">
       <c r="AQ36" s="8" t="s">
         <v>76</v>
       </c>
@@ -3642,7 +4736,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="38" spans="1:43" ht="15" thickBot="1">
+    <row r="38" spans="1:43" ht="15.75" thickBot="1">
       <c r="AQ38" s="13" t="s">
         <v>101</v>
       </c>
@@ -3652,7 +4746,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="40" spans="1:43" ht="15">
+    <row r="40" spans="1:43">
       <c r="A40" s="21" t="s">
         <v>103</v>
       </c>
@@ -3672,7 +4766,7 @@
       <c r="AA40" s="22"/>
       <c r="AB40" s="22"/>
     </row>
-    <row r="41" spans="1:43" ht="15">
+    <row r="41" spans="1:43">
       <c r="A41" s="13" t="s">
         <v>104</v>
       </c>
@@ -3693,7 +4787,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="44" spans="1:43" ht="15">
+    <row r="44" spans="1:43">
       <c r="A44" s="21" t="s">
         <v>106</v>
       </c>
@@ -3725,7 +4819,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="48" spans="1:43" ht="15">
+    <row r="48" spans="1:43">
       <c r="U48" s="21" t="s">
         <v>115</v>
       </c>
@@ -3757,7 +4851,7 @@
     <row r="52" spans="1:24">
       <c r="U52" s="13"/>
     </row>
-    <row r="53" spans="1:24" ht="15">
+    <row r="53" spans="1:24">
       <c r="U53" s="10" t="s">
         <v>117</v>
       </c>
@@ -3772,7 +4866,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="56" spans="1:24" ht="15" thickBot="1"/>
+    <row r="56" spans="1:24" ht="15.75" thickBot="1"/>
     <row r="57" spans="1:24" s="17" customFormat="1" ht="15.75" thickBot="1">
       <c r="A57" s="16" t="s">
         <v>118</v>
@@ -3781,7 +4875,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="58" spans="1:24" ht="15">
+    <row r="58" spans="1:24">
       <c r="B58" s="11" t="s">
         <v>139</v>
       </c>
@@ -3789,7 +4883,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="59" spans="1:24" ht="15">
+    <row r="59" spans="1:24">
       <c r="B59" s="11" t="s">
         <v>140</v>
       </c>
@@ -3797,7 +4891,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="60" spans="1:24" ht="15">
+    <row r="60" spans="1:24">
       <c r="B60" s="11" t="s">
         <v>119</v>
       </c>
@@ -3805,7 +4899,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="61" spans="1:24" ht="15">
+    <row r="61" spans="1:24">
       <c r="B61" s="11" t="s">
         <v>120</v>
       </c>
@@ -3813,7 +4907,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="62" spans="1:24" ht="15">
+    <row r="62" spans="1:24">
       <c r="B62" s="11" t="s">
         <v>121</v>
       </c>
@@ -3829,783 +4923,587 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B261"/>
-  <sheetFormatPr defaultColWidth="3" defaultRowHeight="14.25"/>
+  <dimension ref="A1:BR60"/>
+  <sheetFormatPr defaultColWidth="3" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="16384" width="3" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15">
+    <row r="1" spans="1:68" ht="15.75" thickBot="1">
       <c r="A1" s="12" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15">
-      <c r="A2" s="12" t="s">
+    <row r="2" spans="1:68" s="17" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A2" s="16" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15">
-      <c r="A3" s="12" t="s">
+    <row r="3" spans="1:68">
+      <c r="A3" s="21" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="15">
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
+      <c r="J3" s="22"/>
+      <c r="K3" s="22"/>
+    </row>
+    <row r="4" spans="1:68">
       <c r="A4" s="8" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="5" spans="1:2">
+      <c r="V4" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="W4" s="22"/>
+      <c r="X4" s="22"/>
+      <c r="Y4" s="22"/>
+      <c r="Z4" s="22"/>
+      <c r="AA4" s="22"/>
+      <c r="AB4" s="22"/>
+      <c r="AC4" s="22"/>
+      <c r="AD4" s="22"/>
+      <c r="AM4" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="AN4" s="22"/>
+      <c r="AO4" s="22"/>
+      <c r="AP4" s="22"/>
+      <c r="AQ4" s="22"/>
+      <c r="AR4" s="22"/>
+      <c r="AS4" s="22"/>
+      <c r="AT4" s="22"/>
+      <c r="AU4" s="22"/>
+      <c r="BE4" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="BF4" s="22"/>
+      <c r="BG4" s="22"/>
+      <c r="BH4" s="22"/>
+      <c r="BI4" s="22"/>
+      <c r="BJ4" s="22"/>
+      <c r="BK4" s="22"/>
+      <c r="BL4" s="22"/>
+      <c r="BM4" s="22"/>
+      <c r="BN4" s="22"/>
+      <c r="BO4" s="22"/>
+      <c r="BP4" s="22"/>
+    </row>
+    <row r="5" spans="1:68">
       <c r="A5" s="13" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="6" spans="1:2">
+      <c r="V5" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM5" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="BE5" s="8" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="6" spans="1:68">
       <c r="A6" s="13" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" ht="15">
+      <c r="V6" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="AM6" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="BE6" s="13" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="7" spans="1:68">
       <c r="A7" s="9" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" ht="15">
+      <c r="V7" s="13" t="s">
+        <v>223</v>
+      </c>
+      <c r="AM7" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="BE7" s="13" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="8" spans="1:68">
       <c r="A8" s="9" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="15">
+    <row r="9" spans="1:68">
       <c r="A9" s="9" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" ht="15">
+      <c r="V9" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="AM9" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="BE9" s="8" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="10" spans="1:68">
       <c r="A10" s="9" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" ht="15">
+      <c r="V10" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="AM10" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="BE10" s="15" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="11" spans="1:68">
+      <c r="V11" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="AM11" s="15" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="12" spans="1:68">
       <c r="A12" s="8" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="13" spans="1:2">
+      <c r="BE12" s="8" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="13" spans="1:68">
       <c r="B13" s="15" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" ht="15">
+      <c r="V13" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="AM13" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="BE13" s="13" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="14" spans="1:68">
+      <c r="V14" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="AM14" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="BE14" s="13" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="15" spans="1:68">
       <c r="A15" s="8" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="16" spans="1:2">
+      <c r="V15" s="13" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="16" spans="1:68">
       <c r="B16" s="15" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:70">
       <c r="B17" s="15" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:70">
       <c r="B18" s="15" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="15">
+    <row r="20" spans="1:70">
       <c r="A20" s="8" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:70">
       <c r="A21" s="13" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:70">
       <c r="A22" s="13" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="15">
-      <c r="A26" s="12" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="15">
-      <c r="A28" s="8" t="s">
+    <row r="23" spans="1:70" ht="15.75" thickBot="1"/>
+    <row r="24" spans="1:70" s="17" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A24" s="16" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="25" spans="1:70">
+      <c r="A25" s="21" t="s">
+        <v>178</v>
+      </c>
+      <c r="B25" s="22"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="22"/>
+      <c r="H25" s="22"/>
+      <c r="T25" s="21" t="s">
+        <v>181</v>
+      </c>
+      <c r="U25" s="22"/>
+      <c r="V25" s="22"/>
+      <c r="W25" s="22"/>
+      <c r="X25" s="22"/>
+      <c r="AL25" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="AM25" s="22"/>
+      <c r="AN25" s="22"/>
+      <c r="AO25" s="22"/>
+      <c r="AP25" s="22"/>
+      <c r="AQ25" s="22"/>
+      <c r="AR25" s="22"/>
+      <c r="AS25" s="22"/>
+      <c r="AT25" s="22"/>
+      <c r="AU25" s="22"/>
+      <c r="AV25" s="22"/>
+      <c r="AW25" s="22"/>
+      <c r="BL25" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="BM25" s="22"/>
+      <c r="BN25" s="22"/>
+      <c r="BO25" s="22"/>
+      <c r="BP25" s="22"/>
+      <c r="BQ25" s="22"/>
+      <c r="BR25" s="22"/>
+    </row>
+    <row r="26" spans="1:70">
+      <c r="A26" s="8" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29" s="13"/>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30" s="13" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31" s="13"/>
-    </row>
-    <row r="32" spans="1:2" ht="15">
-      <c r="A32" s="13" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" ht="15">
-      <c r="A34" s="8" t="s">
+      <c r="T26" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="AL26" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="BL26" s="8" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="27" spans="1:70">
+      <c r="A27" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="T27" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="AL27" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="BL27" s="13" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="28" spans="1:70">
+      <c r="A28" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="T28" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="AL28" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="BL28" s="13" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="29" spans="1:70">
+      <c r="BL29" s="13" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="30" spans="1:70">
+      <c r="A30" s="8" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="15" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" s="15" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" ht="15">
-      <c r="A39" s="8" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" s="13"/>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" s="13" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="13"/>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" s="13" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" ht="15">
-      <c r="A47" s="12" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" ht="15">
-      <c r="A49" s="8" t="s">
+      <c r="T30" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="AL30" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31" spans="1:70">
+      <c r="A31" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="AL31" s="15" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="32" spans="1:70" ht="15.75" thickBot="1"/>
+    <row r="33" spans="1:60" s="17" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A33" s="16" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="34" spans="1:60">
+      <c r="A34" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="B34" s="22"/>
+      <c r="C34" s="22"/>
+      <c r="D34" s="22"/>
+      <c r="E34" s="22"/>
+      <c r="F34" s="22"/>
+      <c r="G34" s="22"/>
+      <c r="H34" s="22"/>
+      <c r="I34" s="22"/>
+      <c r="Q34" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="R34" s="22"/>
+      <c r="S34" s="22"/>
+      <c r="T34" s="22"/>
+      <c r="U34" s="22"/>
+      <c r="V34" s="22"/>
+      <c r="W34" s="22"/>
+      <c r="X34" s="22"/>
+      <c r="Y34" s="22"/>
+      <c r="Z34" s="22"/>
+      <c r="AA34" s="22"/>
+      <c r="AB34" s="22"/>
+      <c r="AC34" s="22"/>
+      <c r="AH34" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="AI34" s="22"/>
+      <c r="AJ34" s="22"/>
+      <c r="AK34" s="22"/>
+      <c r="AL34" s="22"/>
+      <c r="AM34" s="22"/>
+      <c r="AN34" s="22"/>
+      <c r="AO34" s="22"/>
+      <c r="AP34" s="22"/>
+      <c r="AZ34" s="21" t="s">
+        <v>208</v>
+      </c>
+      <c r="BA34" s="22"/>
+      <c r="BB34" s="22"/>
+      <c r="BC34" s="22"/>
+      <c r="BD34" s="22"/>
+      <c r="BE34" s="22"/>
+      <c r="BF34" s="22"/>
+      <c r="BG34" s="22"/>
+      <c r="BH34" s="22"/>
+    </row>
+    <row r="35" spans="1:60">
+      <c r="A35" s="8" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" s="13"/>
-    </row>
-    <row r="51" spans="1:1" ht="15">
+      <c r="Q35" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="AH35" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="AZ35" s="8" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="36" spans="1:60">
+      <c r="A36" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="Q36" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="AH36" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="AZ36" s="13" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="37" spans="1:60">
+      <c r="A37" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q37" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="AH37" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="AZ37" s="13" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="38" spans="1:60">
+      <c r="A38" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="Q38" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="AH38" s="8" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="39" spans="1:60">
+      <c r="A39" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q39" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="AH39" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="AZ39" s="8" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="40" spans="1:60">
+      <c r="A40" s="14" t="s">
+        <v>230</v>
+      </c>
+      <c r="Q40" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="AZ40" s="15" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="42" spans="1:60">
+      <c r="A42" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q42" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="AZ42" s="8" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="43" spans="1:60">
+      <c r="A43" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q43" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="AZ43" s="13" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="44" spans="1:60">
+      <c r="A44" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="AZ44" s="13" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="46" spans="1:60">
+      <c r="A46" s="8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="47" spans="1:60" ht="15.75" thickBot="1"/>
+    <row r="48" spans="1:60" s="17" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A48" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="V48" s="18" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22">
+      <c r="A49" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="V49" s="10" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22">
+      <c r="A50" s="13" t="s">
+        <v>234</v>
+      </c>
+      <c r="V50" s="10" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22">
       <c r="A51" s="13" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1">
-      <c r="A52" s="13"/>
-    </row>
-    <row r="53" spans="1:1">
-      <c r="A53" s="13" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" ht="15">
-      <c r="A55" s="8" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1">
-      <c r="A57" s="15" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1">
-      <c r="A58" s="15" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" ht="15">
-      <c r="A60" s="8" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1">
-      <c r="A61" s="13"/>
-    </row>
-    <row r="62" spans="1:1">
-      <c r="A62" s="13" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" ht="15">
-      <c r="A66" s="12" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" ht="15">
-      <c r="A68" s="8" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1">
-      <c r="A69" s="13"/>
-    </row>
-    <row r="70" spans="1:1" ht="15">
-      <c r="A70" s="13" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1">
-      <c r="A71" s="13"/>
-    </row>
-    <row r="72" spans="1:1">
-      <c r="A72" s="13" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" ht="15">
-      <c r="A74" s="8" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1">
-      <c r="A76" s="15" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" ht="15">
-      <c r="A78" s="8" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1">
-      <c r="A79" s="13"/>
-    </row>
-    <row r="80" spans="1:1">
-      <c r="A80" s="13" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1">
-      <c r="A81" s="13"/>
-    </row>
-    <row r="82" spans="1:1">
-      <c r="A82" s="13" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1" ht="15">
-      <c r="A86" s="12" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1" ht="15">
-      <c r="A88" s="12" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1" ht="15">
-      <c r="A90" s="8" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1">
-      <c r="A91" s="13"/>
-    </row>
-    <row r="92" spans="1:1">
-      <c r="A92" s="13" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1">
-      <c r="A93" s="13"/>
-    </row>
-    <row r="94" spans="1:1">
-      <c r="A94" s="13" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1" ht="15">
-      <c r="A96" s="8" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1">
-      <c r="A98" s="15" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1" ht="15">
-      <c r="A102" s="12" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="104" spans="1:1" ht="15">
-      <c r="A104" s="8" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1">
-      <c r="A105" s="13"/>
-    </row>
-    <row r="106" spans="1:1">
-      <c r="A106" s="13" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="107" spans="1:1">
-      <c r="A107" s="13"/>
-    </row>
-    <row r="108" spans="1:1">
-      <c r="A108" s="13" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="110" spans="1:1">
-      <c r="A110" s="15" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="114" spans="1:1" ht="15">
-      <c r="A114" s="12" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="116" spans="1:1" ht="15">
-      <c r="A116" s="8" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="117" spans="1:1">
-      <c r="A117" s="13"/>
-    </row>
-    <row r="118" spans="1:1" ht="15">
-      <c r="A118" s="13" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="119" spans="1:1">
-      <c r="A119" s="13"/>
-    </row>
-    <row r="120" spans="1:1">
-      <c r="A120" s="13" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="122" spans="1:1" ht="15">
-      <c r="A122" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="124" spans="1:1">
-      <c r="A124" s="15" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="128" spans="1:1" ht="15">
-      <c r="A128" s="12" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="130" spans="1:1" ht="15">
-      <c r="A130" s="8" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="131" spans="1:1">
-      <c r="A131" s="13"/>
-    </row>
-    <row r="132" spans="1:1">
-      <c r="A132" s="13" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="133" spans="1:1">
-      <c r="A133" s="13"/>
-    </row>
-    <row r="134" spans="1:1">
-      <c r="A134" s="13" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="135" spans="1:1">
-      <c r="A135" s="13"/>
-    </row>
-    <row r="136" spans="1:1" ht="15">
-      <c r="A136" s="13" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="140" spans="1:1" ht="15">
-      <c r="A140" s="12" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="142" spans="1:1" ht="15">
-      <c r="A142" s="12" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="144" spans="1:1" ht="15">
-      <c r="A144" s="8" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="145" spans="1:1">
-      <c r="A145" s="13"/>
-    </row>
-    <row r="146" spans="1:1">
-      <c r="A146" s="13" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="147" spans="1:1">
-      <c r="A147" s="13"/>
-    </row>
-    <row r="148" spans="1:1">
-      <c r="A148" s="13" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="149" spans="1:1">
-      <c r="A149" s="13"/>
-    </row>
-    <row r="150" spans="1:1">
-      <c r="A150" s="13"/>
-    </row>
-    <row r="151" spans="1:1">
-      <c r="A151" s="14"/>
-    </row>
-    <row r="152" spans="1:1">
-      <c r="A152" s="14" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="153" spans="1:1">
-      <c r="A153" s="14"/>
-    </row>
-    <row r="154" spans="1:1">
-      <c r="A154" s="14" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="155" spans="1:1">
-      <c r="A155" s="14"/>
-    </row>
-    <row r="156" spans="1:1">
-      <c r="A156" s="14" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="158" spans="1:1" ht="15">
-      <c r="A158" s="8" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="160" spans="1:1">
-      <c r="A160" s="15" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="161" spans="1:1">
-      <c r="A161" s="15" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="163" spans="1:1" ht="15">
-      <c r="A163" s="8" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="167" spans="1:1" ht="15">
-      <c r="A167" s="12" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="169" spans="1:1" ht="15">
-      <c r="A169" s="8" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="170" spans="1:1">
-      <c r="A170" s="13"/>
-    </row>
-    <row r="171" spans="1:1">
-      <c r="A171" s="13" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="172" spans="1:1">
-      <c r="A172" s="13"/>
-    </row>
-    <row r="173" spans="1:1">
-      <c r="A173" s="13"/>
-    </row>
-    <row r="174" spans="1:1">
-      <c r="A174" s="14"/>
-    </row>
-    <row r="175" spans="1:1">
-      <c r="A175" s="14" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="176" spans="1:1">
-      <c r="A176" s="14"/>
-    </row>
-    <row r="177" spans="1:1">
-      <c r="A177" s="14" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="178" spans="1:1">
-      <c r="A178" s="14"/>
-    </row>
-    <row r="179" spans="1:1">
-      <c r="A179" s="14" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="180" spans="1:1">
-      <c r="A180" s="14"/>
-    </row>
-    <row r="181" spans="1:1">
-      <c r="A181" s="14" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="183" spans="1:1" ht="15">
-      <c r="A183" s="8" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="185" spans="1:1">
-      <c r="A185" s="15" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="189" spans="1:1" ht="15">
-      <c r="A189" s="12" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="191" spans="1:1" ht="15">
-      <c r="A191" s="8" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="192" spans="1:1">
-      <c r="A192" s="13"/>
-    </row>
-    <row r="193" spans="1:1" ht="15">
-      <c r="A193" s="13" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="194" spans="1:1">
-      <c r="A194" s="13"/>
-    </row>
-    <row r="195" spans="1:1">
-      <c r="A195" s="13" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="197" spans="1:1" ht="15">
-      <c r="A197" s="8" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="199" spans="1:1">
-      <c r="A199" s="15" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="203" spans="1:1" ht="15">
-      <c r="A203" s="12" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="205" spans="1:1" ht="15">
-      <c r="A205" s="8" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="206" spans="1:1">
-      <c r="A206" s="13"/>
-    </row>
-    <row r="207" spans="1:1" ht="15">
-      <c r="A207" s="13" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="208" spans="1:1">
-      <c r="A208" s="13"/>
-    </row>
-    <row r="209" spans="1:1">
-      <c r="A209" s="13" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="211" spans="1:1" ht="15">
-      <c r="A211" s="8" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="213" spans="1:1">
-      <c r="A213" s="15" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="215" spans="1:1" ht="15">
-      <c r="A215" s="8" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="216" spans="1:1">
-      <c r="A216" s="13"/>
-    </row>
-    <row r="217" spans="1:1">
-      <c r="A217" s="13" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="218" spans="1:1">
-      <c r="A218" s="13"/>
-    </row>
-    <row r="219" spans="1:1">
-      <c r="A219" s="13" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="223" spans="1:1" ht="15">
-      <c r="A223" s="12" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="225" spans="1:1">
-      <c r="A225" s="11" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="226" spans="1:1">
-      <c r="A226" s="13"/>
-    </row>
-    <row r="227" spans="1:1" ht="15">
-      <c r="A227" s="13" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="228" spans="1:1">
-      <c r="A228" s="13"/>
-    </row>
-    <row r="229" spans="1:1" ht="15">
-      <c r="A229" s="13" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="231" spans="1:1">
-      <c r="A231" s="11" t="s">
+      <c r="V51" s="10" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22">
+      <c r="V52" s="10" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22">
+      <c r="A53" s="11" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="232" spans="1:1">
-      <c r="A232" s="13"/>
-    </row>
-    <row r="233" spans="1:1" ht="15">
-      <c r="A233" s="13" t="s">
+      <c r="V53" s="10" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22">
+      <c r="A54" s="13" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="235" spans="1:1">
-      <c r="A235" s="11" t="s">
+      <c r="V54" s="10" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="56" spans="1:22">
+      <c r="A56" s="11" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="236" spans="1:1">
-      <c r="A236" s="13"/>
-    </row>
-    <row r="237" spans="1:1" ht="15">
-      <c r="A237" s="13" t="s">
+    <row r="57" spans="1:22">
+      <c r="A57" s="13" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="239" spans="1:1">
-      <c r="A239" s="11" t="s">
+    <row r="59" spans="1:22">
+      <c r="A59" s="11" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="240" spans="1:1">
-      <c r="A240" s="13"/>
-    </row>
-    <row r="241" spans="1:1" ht="15">
-      <c r="A241" s="10" t="s">
+    <row r="60" spans="1:22">
+      <c r="A60" s="10" t="s">
         <v>238</v>
-      </c>
-    </row>
-    <row r="245" spans="1:1" ht="15">
-      <c r="A245" s="12" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="246" spans="1:1">
-      <c r="A246" s="13"/>
-    </row>
-    <row r="247" spans="1:1" ht="15">
-      <c r="A247" s="10" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="248" spans="1:1">
-      <c r="A248" s="13"/>
-    </row>
-    <row r="249" spans="1:1" ht="15">
-      <c r="A249" s="10" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="250" spans="1:1">
-      <c r="A250" s="13"/>
-    </row>
-    <row r="251" spans="1:1" ht="15">
-      <c r="A251" s="10" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="252" spans="1:1">
-      <c r="A252" s="13"/>
-    </row>
-    <row r="253" spans="1:1" ht="15">
-      <c r="A253" s="10" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="254" spans="1:1">
-      <c r="A254" s="13"/>
-    </row>
-    <row r="255" spans="1:1" ht="15">
-      <c r="A255" s="10" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="256" spans="1:1">
-      <c r="A256" s="13"/>
-    </row>
-    <row r="257" spans="1:1" ht="15">
-      <c r="A257" s="10" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="261" spans="1:1" ht="15">
-      <c r="A261" s="11" t="s">
-        <v>245</v>
       </c>
     </row>
   </sheetData>
@@ -4615,9 +5513,533 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="3" defaultRowHeight="14.25"/>
-  <sheetData/>
+  <dimension ref="A1:CD52"/>
+  <sheetFormatPr defaultColWidth="3" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="16384" width="3" style="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:82" ht="15.75" thickBot="1">
+      <c r="A1" s="12" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="2" spans="1:82" s="17" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A2" s="16" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="3" spans="1:82">
+      <c r="A3" s="21" t="s">
+        <v>319</v>
+      </c>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="X3" s="21" t="s">
+        <v>325</v>
+      </c>
+      <c r="Y3" s="22"/>
+      <c r="Z3" s="22"/>
+      <c r="AA3" s="22"/>
+      <c r="AB3" s="22"/>
+      <c r="AC3" s="22"/>
+      <c r="AD3" s="22"/>
+      <c r="AW3" s="21" t="s">
+        <v>268</v>
+      </c>
+      <c r="AX3" s="22"/>
+      <c r="AY3" s="22"/>
+      <c r="AZ3" s="22"/>
+      <c r="BA3" s="22"/>
+      <c r="BB3" s="22"/>
+      <c r="BC3" s="22"/>
+      <c r="BD3" s="22"/>
+      <c r="BW3" s="21" t="s">
+        <v>280</v>
+      </c>
+      <c r="BX3" s="22"/>
+      <c r="BY3" s="22"/>
+      <c r="BZ3" s="22"/>
+      <c r="CA3" s="22"/>
+      <c r="CB3" s="22"/>
+      <c r="CC3" s="22"/>
+      <c r="CD3" s="22"/>
+    </row>
+    <row r="4" spans="1:82">
+      <c r="A4" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="X4" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="AW4" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="BW4" s="8" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="5" spans="1:82">
+      <c r="A5" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="X5" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="AW5" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="BW5" s="25" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="6" spans="1:82">
+      <c r="A6" s="13" t="s">
+        <v>320</v>
+      </c>
+      <c r="X6" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="AW6" s="13" t="s">
+        <v>326</v>
+      </c>
+      <c r="BW6" s="25" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="8" spans="1:82">
+      <c r="A8" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="X8" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="AW8" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="BW8" s="8" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="9" spans="1:82">
+      <c r="A9" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="X9" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="AW9" s="13" t="s">
+        <v>271</v>
+      </c>
+      <c r="BW9" s="15" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="10" spans="1:82">
+      <c r="B10" s="23" t="s">
+        <v>248</v>
+      </c>
+      <c r="X10" s="15" t="s">
+        <v>259</v>
+      </c>
+      <c r="AW10" s="23" t="s">
+        <v>272</v>
+      </c>
+      <c r="BW10" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:82">
+      <c r="A11" s="13" t="s">
+        <v>322</v>
+      </c>
+      <c r="X11" s="15" t="s">
+        <v>260</v>
+      </c>
+      <c r="BW11" s="24"/>
+    </row>
+    <row r="12" spans="1:82">
+      <c r="A12" s="13" t="s">
+        <v>323</v>
+      </c>
+      <c r="AW12" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="BW12" s="15" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="13" spans="1:82">
+      <c r="B13" s="23" t="s">
+        <v>249</v>
+      </c>
+      <c r="X13" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="AW13" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="BW13" s="15" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="14" spans="1:82">
+      <c r="X14" s="13" t="s">
+        <v>262</v>
+      </c>
+      <c r="AW14" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="BW14" s="15" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="15" spans="1:82">
+      <c r="A15" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="X15" s="23" t="s">
+        <v>263</v>
+      </c>
+      <c r="AW15" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="BW15" s="15" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="16" spans="1:82">
+      <c r="A16" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="BW16" s="15" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:75">
+      <c r="A17" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="X17" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="AW17" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="BW17" s="24"/>
+    </row>
+    <row r="18" spans="1:75">
+      <c r="X18" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="AW18" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="BW18" s="15" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="19" spans="1:75">
+      <c r="A19" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="X19" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="AW19" s="13" t="s">
+        <v>278</v>
+      </c>
+      <c r="BW19" s="15" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="20" spans="1:75">
+      <c r="A20" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="BW20" s="15" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="21" spans="1:75">
+      <c r="A21" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="X21" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="AW21" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="BW21" s="15" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="22" spans="1:75">
+      <c r="X22" s="13" t="s">
+        <v>266</v>
+      </c>
+      <c r="AW22" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="BW22" s="15" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="23" spans="1:75">
+      <c r="A23" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="X23" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="AW23" s="13" t="s">
+        <v>327</v>
+      </c>
+      <c r="BW23" s="15" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="24" spans="1:75">
+      <c r="A24" s="13" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="25" spans="1:75">
+      <c r="A25" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="BW25" s="8" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="26" spans="1:75">
+      <c r="BW26" s="13" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="27" spans="1:75">
+      <c r="BW27" s="13" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="29" spans="1:75">
+      <c r="BW29" s="8" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="30" spans="1:75">
+      <c r="BW30" s="13" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="31" spans="1:75" ht="15.75" thickBot="1">
+      <c r="BW31" s="13" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="32" spans="1:75" s="17" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A32" s="16" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="33" spans="1:72">
+      <c r="A33" s="21" t="s">
+        <v>296</v>
+      </c>
+      <c r="B33" s="22"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="22"/>
+      <c r="H33" s="22"/>
+      <c r="V33" s="21" t="s">
+        <v>301</v>
+      </c>
+      <c r="W33" s="22"/>
+      <c r="X33" s="22"/>
+      <c r="Y33" s="22"/>
+      <c r="Z33" s="22"/>
+      <c r="AA33" s="22"/>
+      <c r="AB33" s="22"/>
+      <c r="AC33" s="22"/>
+      <c r="AD33" s="22"/>
+      <c r="AN33" s="21" t="s">
+        <v>307</v>
+      </c>
+      <c r="AO33" s="22"/>
+      <c r="AP33" s="22"/>
+      <c r="AQ33" s="22"/>
+      <c r="AR33" s="22"/>
+      <c r="AS33" s="22"/>
+      <c r="AT33" s="22"/>
+      <c r="AU33" s="22"/>
+      <c r="BM33" s="21" t="s">
+        <v>314</v>
+      </c>
+      <c r="BN33" s="22"/>
+      <c r="BO33" s="22"/>
+      <c r="BP33" s="22"/>
+      <c r="BQ33" s="22"/>
+      <c r="BR33" s="22"/>
+      <c r="BS33" s="22"/>
+      <c r="BT33" s="22"/>
+    </row>
+    <row r="34" spans="1:72">
+      <c r="A34" s="13" t="s">
+        <v>297</v>
+      </c>
+      <c r="V34" s="13" t="s">
+        <v>330</v>
+      </c>
+      <c r="AN34" s="13" t="s">
+        <v>308</v>
+      </c>
+      <c r="BM34" s="13" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="35" spans="1:72">
+      <c r="A35" s="13" t="s">
+        <v>328</v>
+      </c>
+      <c r="V35" s="13" t="s">
+        <v>331</v>
+      </c>
+      <c r="AN35" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="BM35" s="13" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="37" spans="1:72">
+      <c r="A37" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="V37" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="AN37" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="BM37" s="8" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="38" spans="1:72">
+      <c r="A38" s="15" t="s">
+        <v>298</v>
+      </c>
+      <c r="V38" s="15" t="s">
+        <v>303</v>
+      </c>
+      <c r="AN38" s="15" t="s">
+        <v>309</v>
+      </c>
+      <c r="BM38" s="15" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="39" spans="1:72">
+      <c r="A39" s="11" t="s">
+        <v>299</v>
+      </c>
+      <c r="V39" s="15" t="s">
+        <v>304</v>
+      </c>
+      <c r="AN39" s="11" t="s">
+        <v>310</v>
+      </c>
+      <c r="BM39" s="11" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="41" spans="1:72">
+      <c r="A41" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="V41" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="AN41" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="BM41" s="8" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="42" spans="1:72">
+      <c r="A42" s="13" t="s">
+        <v>300</v>
+      </c>
+      <c r="V42" s="13" t="s">
+        <v>305</v>
+      </c>
+      <c r="AN42" s="13" t="s">
+        <v>311</v>
+      </c>
+      <c r="BM42" s="13" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="43" spans="1:72">
+      <c r="V43" s="13" t="s">
+        <v>306</v>
+      </c>
+      <c r="AN43" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="BM43" s="13" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="44" spans="1:72">
+      <c r="AN44" s="9" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="45" spans="1:72">
+      <c r="AN45" s="14" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="46" spans="1:72" ht="15.75" thickBot="1"/>
+    <row r="47" spans="1:72" s="17" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A47" s="16" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="48" spans="1:72">
+      <c r="A48" s="10" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="10" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="10" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="10" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="10" t="s">
+        <v>342</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>